--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8352,6 +8352,248 @@
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>115069908</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57653</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>760097</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7452559</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>115070971</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57919</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>758931</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7454231</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8594,6 +8594,853 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>115067594</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>759945</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7452754</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>115067584</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>759321</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7453501</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>115067034</v>
+      </c>
+      <c r="B74" t="n">
+        <v>56705</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>759760</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7452993</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>115067595</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>758897</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7454237</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>115067032</v>
+      </c>
+      <c r="B76" t="n">
+        <v>56705</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>759539</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7453172</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>115067578</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57888</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>759053</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7454072</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>115067620</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57857</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>759456</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7453280</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9441,6 +9441,369 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>115069485</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57346</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>759181</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7453801</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>115115980</v>
+      </c>
+      <c r="B80" t="n">
+        <v>56456</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>759506</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7453271</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>115115982</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57346</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Aitik, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>759174</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7453748</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Via Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,7 +9806,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294734</v>
+        <v>122294751</v>
       </c>
       <c r="B82" t="n">
         <v>98175</v>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>759440</v>
+        <v>759473</v>
       </c>
       <c r="R82" t="n">
-        <v>7453257</v>
+        <v>7453318</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,7 +9927,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294733</v>
+        <v>122294755</v>
       </c>
       <c r="B83" t="n">
         <v>98175</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>759435</v>
+        <v>760091</v>
       </c>
       <c r="R83" t="n">
-        <v>7453258</v>
+        <v>7452637</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10011,17 +10011,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,7 +10048,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294748</v>
+        <v>122294742</v>
       </c>
       <c r="B84" t="n">
         <v>98175</v>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>759459</v>
+        <v>759446</v>
       </c>
       <c r="R84" t="n">
-        <v>7453317</v>
+        <v>7453326</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,7 +10169,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294742</v>
+        <v>122294732</v>
       </c>
       <c r="B85" t="n">
         <v>98175</v>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759446</v>
+        <v>759420</v>
       </c>
       <c r="R85" t="n">
-        <v>7453326</v>
+        <v>7453262</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,7 +10290,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294736</v>
+        <v>122294753</v>
       </c>
       <c r="B86" t="n">
         <v>98175</v>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759442</v>
+        <v>759466</v>
       </c>
       <c r="R86" t="n">
-        <v>7453258</v>
+        <v>7453312</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,7 +10411,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294666</v>
+        <v>122294754</v>
       </c>
       <c r="B87" t="n">
         <v>98175</v>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>759423</v>
+        <v>760088</v>
       </c>
       <c r="R87" t="n">
-        <v>7453284</v>
+        <v>7452640</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10495,17 +10495,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294754</v>
+        <v>122294736</v>
       </c>
       <c r="B88" t="n">
         <v>98175</v>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>760088</v>
+        <v>759442</v>
       </c>
       <c r="R88" t="n">
-        <v>7452640</v>
+        <v>7453258</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10616,17 +10616,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,7 +10653,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294745</v>
+        <v>122294748</v>
       </c>
       <c r="B89" t="n">
         <v>98175</v>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>759454</v>
+        <v>759459</v>
       </c>
       <c r="R89" t="n">
-        <v>7453307</v>
+        <v>7453317</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10774,7 +10774,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294752</v>
+        <v>122294750</v>
       </c>
       <c r="B90" t="n">
         <v>98175</v>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759463</v>
+        <v>759475</v>
       </c>
       <c r="R90" t="n">
-        <v>7453317</v>
+        <v>7453308</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,7 +10895,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294739</v>
+        <v>122294733</v>
       </c>
       <c r="B91" t="n">
         <v>98175</v>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759446</v>
+        <v>759435</v>
       </c>
       <c r="R91" t="n">
-        <v>7453342</v>
+        <v>7453258</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,7 +11016,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294744</v>
+        <v>122294746</v>
       </c>
       <c r="B92" t="n">
         <v>98175</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>759458</v>
+        <v>759454</v>
       </c>
       <c r="R92" t="n">
-        <v>7453299</v>
+        <v>7453310</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,7 +11137,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294755</v>
+        <v>122294747</v>
       </c>
       <c r="B93" t="n">
         <v>98175</v>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>760091</v>
+        <v>759454</v>
       </c>
       <c r="R93" t="n">
-        <v>7452637</v>
+        <v>7453307</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11221,17 +11221,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,7 +11258,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294751</v>
+        <v>122294666</v>
       </c>
       <c r="B94" t="n">
         <v>98175</v>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759473</v>
+        <v>759423</v>
       </c>
       <c r="R94" t="n">
-        <v>7453318</v>
+        <v>7453284</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11342,17 +11342,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294746</v>
+        <v>122294734</v>
       </c>
       <c r="B95" t="n">
         <v>98175</v>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759454</v>
+        <v>759440</v>
       </c>
       <c r="R95" t="n">
-        <v>7453310</v>
+        <v>7453257</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11500,7 +11500,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294737</v>
+        <v>122294741</v>
       </c>
       <c r="B96" t="n">
         <v>98175</v>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759443</v>
+        <v>759446</v>
       </c>
       <c r="R96" t="n">
-        <v>7453255</v>
+        <v>7453323</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,7 +11621,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294735</v>
+        <v>122294737</v>
       </c>
       <c r="B97" t="n">
         <v>98175</v>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759441</v>
+        <v>759443</v>
       </c>
       <c r="R97" t="n">
-        <v>7453256</v>
+        <v>7453255</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,7 +11742,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294743</v>
+        <v>122294749</v>
       </c>
       <c r="B98" t="n">
         <v>98175</v>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759443</v>
+        <v>759478</v>
       </c>
       <c r="R98" t="n">
-        <v>7453311</v>
+        <v>7453303</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,7 +11863,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294750</v>
+        <v>122294744</v>
       </c>
       <c r="B99" t="n">
         <v>98175</v>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759475</v>
+        <v>759458</v>
       </c>
       <c r="R99" t="n">
-        <v>7453308</v>
+        <v>7453299</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11984,7 +11984,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294753</v>
+        <v>122294735</v>
       </c>
       <c r="B100" t="n">
         <v>98175</v>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12038,10 +12038,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>759466</v>
+        <v>759441</v>
       </c>
       <c r="R100" t="n">
-        <v>7453312</v>
+        <v>7453256</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12105,7 +12105,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294738</v>
+        <v>122294752</v>
       </c>
       <c r="B101" t="n">
         <v>98175</v>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12159,10 +12159,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759436</v>
+        <v>759463</v>
       </c>
       <c r="R101" t="n">
-        <v>7453325</v>
+        <v>7453317</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12226,7 +12226,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294749</v>
+        <v>122294740</v>
       </c>
       <c r="B102" t="n">
         <v>98175</v>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759478</v>
+        <v>759438</v>
       </c>
       <c r="R102" t="n">
-        <v>7453303</v>
+        <v>7453321</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12347,7 +12347,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294732</v>
+        <v>122294738</v>
       </c>
       <c r="B103" t="n">
         <v>98175</v>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>759420</v>
+        <v>759436</v>
       </c>
       <c r="R103" t="n">
-        <v>7453262</v>
+        <v>7453325</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12441,7 +12441,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12468,7 +12468,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294740</v>
+        <v>122294739</v>
       </c>
       <c r="B104" t="n">
         <v>98175</v>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>759438</v>
+        <v>759446</v>
       </c>
       <c r="R104" t="n">
-        <v>7453321</v>
+        <v>7453342</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12589,7 +12589,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294741</v>
+        <v>122294743</v>
       </c>
       <c r="B105" t="n">
         <v>98175</v>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759446</v>
+        <v>759443</v>
       </c>
       <c r="R105" t="n">
-        <v>7453323</v>
+        <v>7453311</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -10774,7 +10774,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294750</v>
+        <v>122294733</v>
       </c>
       <c r="B90" t="n">
         <v>98175</v>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759475</v>
+        <v>759435</v>
       </c>
       <c r="R90" t="n">
-        <v>7453308</v>
+        <v>7453258</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,7 +10895,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294733</v>
+        <v>122294750</v>
       </c>
       <c r="B91" t="n">
         <v>98175</v>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759435</v>
+        <v>759475</v>
       </c>
       <c r="R91" t="n">
-        <v>7453258</v>
+        <v>7453308</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,7 +11016,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294746</v>
+        <v>122294747</v>
       </c>
       <c r="B92" t="n">
         <v>98175</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11073,7 +11073,7 @@
         <v>759454</v>
       </c>
       <c r="R92" t="n">
-        <v>7453310</v>
+        <v>7453307</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,7 +11137,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294747</v>
+        <v>122294746</v>
       </c>
       <c r="B93" t="n">
         <v>98175</v>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11194,7 +11194,7 @@
         <v>759454</v>
       </c>
       <c r="R93" t="n">
-        <v>7453307</v>
+        <v>7453310</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD93" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,10 +9806,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294751</v>
+        <v>122294741</v>
       </c>
       <c r="B82" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>759473</v>
+        <v>759446</v>
       </c>
       <c r="R82" t="n">
-        <v>7453318</v>
+        <v>7453323</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,10 +9927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294755</v>
+        <v>122294754</v>
       </c>
       <c r="B83" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>760091</v>
+        <v>760088</v>
       </c>
       <c r="R83" t="n">
-        <v>7452637</v>
+        <v>7452640</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,10 +10048,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294742</v>
+        <v>122294745</v>
       </c>
       <c r="B84" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>759446</v>
+        <v>759454</v>
       </c>
       <c r="R84" t="n">
-        <v>7453326</v>
+        <v>7453307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,10 +10169,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294732</v>
+        <v>122294753</v>
       </c>
       <c r="B85" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759420</v>
+        <v>759466</v>
       </c>
       <c r="R85" t="n">
-        <v>7453262</v>
+        <v>7453312</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,10 +10290,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294753</v>
+        <v>122294732</v>
       </c>
       <c r="B86" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759466</v>
+        <v>759420</v>
       </c>
       <c r="R86" t="n">
-        <v>7453312</v>
+        <v>7453262</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,10 +10411,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294754</v>
+        <v>122294746</v>
       </c>
       <c r="B87" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>760088</v>
+        <v>759454</v>
       </c>
       <c r="R87" t="n">
-        <v>7452640</v>
+        <v>7453310</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10495,17 +10495,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,10 +10532,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294736</v>
+        <v>122294750</v>
       </c>
       <c r="B88" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759442</v>
+        <v>759475</v>
       </c>
       <c r="R88" t="n">
-        <v>7453258</v>
+        <v>7453308</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294748</v>
+        <v>122294755</v>
       </c>
       <c r="B89" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>759459</v>
+        <v>760091</v>
       </c>
       <c r="R89" t="n">
-        <v>7453317</v>
+        <v>7452637</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10737,17 +10737,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294733</v>
+        <v>122294742</v>
       </c>
       <c r="B90" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759435</v>
+        <v>759446</v>
       </c>
       <c r="R90" t="n">
-        <v>7453258</v>
+        <v>7453326</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,10 +10895,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294750</v>
+        <v>122294744</v>
       </c>
       <c r="B91" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759475</v>
+        <v>759458</v>
       </c>
       <c r="R91" t="n">
-        <v>7453308</v>
+        <v>7453299</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294747</v>
+        <v>122294666</v>
       </c>
       <c r="B92" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>759454</v>
+        <v>759423</v>
       </c>
       <c r="R92" t="n">
-        <v>7453307</v>
+        <v>7453284</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11100,17 +11100,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,10 +11137,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294746</v>
+        <v>122294748</v>
       </c>
       <c r="B93" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759454</v>
+        <v>759459</v>
       </c>
       <c r="R93" t="n">
-        <v>7453310</v>
+        <v>7453317</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,10 +11258,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294666</v>
+        <v>122294735</v>
       </c>
       <c r="B94" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759423</v>
+        <v>759441</v>
       </c>
       <c r="R94" t="n">
-        <v>7453284</v>
+        <v>7453256</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11342,17 +11342,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11379,10 +11379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294734</v>
+        <v>122294736</v>
       </c>
       <c r="B95" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759440</v>
+        <v>759442</v>
       </c>
       <c r="R95" t="n">
-        <v>7453257</v>
+        <v>7453258</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11500,10 +11500,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294741</v>
+        <v>122294749</v>
       </c>
       <c r="B96" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759446</v>
+        <v>759478</v>
       </c>
       <c r="R96" t="n">
-        <v>7453323</v>
+        <v>7453303</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,10 +11621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294737</v>
+        <v>122294743</v>
       </c>
       <c r="B97" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11678,7 +11678,7 @@
         <v>759443</v>
       </c>
       <c r="R97" t="n">
-        <v>7453255</v>
+        <v>7453311</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,10 +11742,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294749</v>
+        <v>122294737</v>
       </c>
       <c r="B98" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759478</v>
+        <v>759443</v>
       </c>
       <c r="R98" t="n">
-        <v>7453303</v>
+        <v>7453255</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,10 +11863,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294744</v>
+        <v>122294733</v>
       </c>
       <c r="B99" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759458</v>
+        <v>759435</v>
       </c>
       <c r="R99" t="n">
-        <v>7453299</v>
+        <v>7453258</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11984,10 +11984,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294735</v>
+        <v>122294738</v>
       </c>
       <c r="B100" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12038,10 +12038,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>759441</v>
+        <v>759436</v>
       </c>
       <c r="R100" t="n">
-        <v>7453256</v>
+        <v>7453325</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12105,10 +12105,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294752</v>
+        <v>122294751</v>
       </c>
       <c r="B101" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12159,10 +12159,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759463</v>
+        <v>759473</v>
       </c>
       <c r="R101" t="n">
-        <v>7453317</v>
+        <v>7453318</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12226,10 +12226,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294740</v>
+        <v>122294752</v>
       </c>
       <c r="B102" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759438</v>
+        <v>759463</v>
       </c>
       <c r="R102" t="n">
-        <v>7453321</v>
+        <v>7453317</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12347,10 +12347,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294738</v>
+        <v>122294739</v>
       </c>
       <c r="B103" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>759436</v>
+        <v>759446</v>
       </c>
       <c r="R103" t="n">
-        <v>7453325</v>
+        <v>7453342</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12441,7 +12441,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12468,10 +12468,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294739</v>
+        <v>122294740</v>
       </c>
       <c r="B104" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>759446</v>
+        <v>759438</v>
       </c>
       <c r="R104" t="n">
-        <v>7453342</v>
+        <v>7453321</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12589,10 +12589,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294743</v>
+        <v>122294734</v>
       </c>
       <c r="B105" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759443</v>
+        <v>759440</v>
       </c>
       <c r="R105" t="n">
-        <v>7453311</v>
+        <v>7453257</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,7 +9806,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294741</v>
+        <v>122294742</v>
       </c>
       <c r="B82" t="n">
         <v>98185</v>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9863,7 +9863,7 @@
         <v>759446</v>
       </c>
       <c r="R82" t="n">
-        <v>7453323</v>
+        <v>7453326</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,7 +9927,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294754</v>
+        <v>122294738</v>
       </c>
       <c r="B83" t="n">
         <v>98185</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>760088</v>
+        <v>759436</v>
       </c>
       <c r="R83" t="n">
-        <v>7452640</v>
+        <v>7453325</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10011,17 +10011,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,7 +10048,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294745</v>
+        <v>122294754</v>
       </c>
       <c r="B84" t="n">
         <v>98185</v>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>759454</v>
+        <v>760088</v>
       </c>
       <c r="R84" t="n">
-        <v>7453307</v>
+        <v>7452640</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10132,17 +10132,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,7 +10169,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294753</v>
+        <v>122294735</v>
       </c>
       <c r="B85" t="n">
         <v>98185</v>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759466</v>
+        <v>759441</v>
       </c>
       <c r="R85" t="n">
-        <v>7453312</v>
+        <v>7453256</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,7 +10290,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294732</v>
+        <v>122294737</v>
       </c>
       <c r="B86" t="n">
         <v>98185</v>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759420</v>
+        <v>759443</v>
       </c>
       <c r="R86" t="n">
-        <v>7453262</v>
+        <v>7453255</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,7 +10411,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294746</v>
+        <v>122294750</v>
       </c>
       <c r="B87" t="n">
         <v>98185</v>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>759454</v>
+        <v>759475</v>
       </c>
       <c r="R87" t="n">
-        <v>7453310</v>
+        <v>7453308</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294750</v>
+        <v>122294732</v>
       </c>
       <c r="B88" t="n">
         <v>98185</v>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759475</v>
+        <v>759420</v>
       </c>
       <c r="R88" t="n">
-        <v>7453308</v>
+        <v>7453262</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,7 +10653,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294755</v>
+        <v>122294748</v>
       </c>
       <c r="B89" t="n">
         <v>98185</v>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>760091</v>
+        <v>759459</v>
       </c>
       <c r="R89" t="n">
-        <v>7452637</v>
+        <v>7453317</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10737,17 +10737,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10774,7 +10774,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294742</v>
+        <v>122294741</v>
       </c>
       <c r="B90" t="n">
         <v>98185</v>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10831,7 +10831,7 @@
         <v>759446</v>
       </c>
       <c r="R90" t="n">
-        <v>7453326</v>
+        <v>7453323</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,7 +10895,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294744</v>
+        <v>122294736</v>
       </c>
       <c r="B91" t="n">
         <v>98185</v>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759458</v>
+        <v>759442</v>
       </c>
       <c r="R91" t="n">
-        <v>7453299</v>
+        <v>7453258</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,7 +11016,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294666</v>
+        <v>122294733</v>
       </c>
       <c r="B92" t="n">
         <v>98185</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>759423</v>
+        <v>759435</v>
       </c>
       <c r="R92" t="n">
-        <v>7453284</v>
+        <v>7453258</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11100,17 +11100,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,7 +11137,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294748</v>
+        <v>122294743</v>
       </c>
       <c r="B93" t="n">
         <v>98185</v>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759459</v>
+        <v>759443</v>
       </c>
       <c r="R93" t="n">
-        <v>7453317</v>
+        <v>7453311</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,7 +11258,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294735</v>
+        <v>122294753</v>
       </c>
       <c r="B94" t="n">
         <v>98185</v>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759441</v>
+        <v>759466</v>
       </c>
       <c r="R94" t="n">
-        <v>7453256</v>
+        <v>7453312</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294736</v>
+        <v>122294749</v>
       </c>
       <c r="B95" t="n">
         <v>98185</v>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759442</v>
+        <v>759478</v>
       </c>
       <c r="R95" t="n">
-        <v>7453258</v>
+        <v>7453303</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11500,7 +11500,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294749</v>
+        <v>122294740</v>
       </c>
       <c r="B96" t="n">
         <v>98185</v>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759478</v>
+        <v>759438</v>
       </c>
       <c r="R96" t="n">
-        <v>7453303</v>
+        <v>7453321</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,7 +11621,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294743</v>
+        <v>122294746</v>
       </c>
       <c r="B97" t="n">
         <v>98185</v>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759443</v>
+        <v>759454</v>
       </c>
       <c r="R97" t="n">
-        <v>7453311</v>
+        <v>7453310</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,7 +11742,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294737</v>
+        <v>122294751</v>
       </c>
       <c r="B98" t="n">
         <v>98185</v>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759443</v>
+        <v>759473</v>
       </c>
       <c r="R98" t="n">
-        <v>7453255</v>
+        <v>7453318</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,7 +11863,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294733</v>
+        <v>122294666</v>
       </c>
       <c r="B99" t="n">
         <v>98185</v>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759435</v>
+        <v>759423</v>
       </c>
       <c r="R99" t="n">
-        <v>7453258</v>
+        <v>7453284</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11947,17 +11947,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11984,7 +11984,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294738</v>
+        <v>122294734</v>
       </c>
       <c r="B100" t="n">
         <v>98185</v>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12038,10 +12038,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>759436</v>
+        <v>759440</v>
       </c>
       <c r="R100" t="n">
-        <v>7453325</v>
+        <v>7453257</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12105,7 +12105,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294751</v>
+        <v>122294744</v>
       </c>
       <c r="B101" t="n">
         <v>98185</v>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12159,10 +12159,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759473</v>
+        <v>759458</v>
       </c>
       <c r="R101" t="n">
-        <v>7453318</v>
+        <v>7453299</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12226,7 +12226,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294752</v>
+        <v>122294745</v>
       </c>
       <c r="B102" t="n">
         <v>98185</v>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759463</v>
+        <v>759454</v>
       </c>
       <c r="R102" t="n">
-        <v>7453317</v>
+        <v>7453307</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12347,7 +12347,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294739</v>
+        <v>122294755</v>
       </c>
       <c r="B103" t="n">
         <v>98185</v>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>759446</v>
+        <v>760091</v>
       </c>
       <c r="R103" t="n">
-        <v>7453342</v>
+        <v>7452637</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12431,17 +12431,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12468,7 +12468,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294740</v>
+        <v>122294752</v>
       </c>
       <c r="B104" t="n">
         <v>98185</v>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>759438</v>
+        <v>759463</v>
       </c>
       <c r="R104" t="n">
-        <v>7453321</v>
+        <v>7453317</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12589,7 +12589,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294734</v>
+        <v>122294739</v>
       </c>
       <c r="B105" t="n">
         <v>98185</v>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759440</v>
+        <v>759446</v>
       </c>
       <c r="R105" t="n">
-        <v>7453257</v>
+        <v>7453342</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -11621,7 +11621,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294746</v>
+        <v>122294751</v>
       </c>
       <c r="B97" t="n">
         <v>98185</v>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759454</v>
+        <v>759473</v>
       </c>
       <c r="R97" t="n">
-        <v>7453310</v>
+        <v>7453318</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,7 +11742,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294751</v>
+        <v>122294746</v>
       </c>
       <c r="B98" t="n">
         <v>98185</v>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759473</v>
+        <v>759454</v>
       </c>
       <c r="R98" t="n">
-        <v>7453318</v>
+        <v>7453310</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,10 +9806,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294742</v>
+        <v>122294741</v>
       </c>
       <c r="B82" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9863,7 +9863,7 @@
         <v>759446</v>
       </c>
       <c r="R82" t="n">
-        <v>7453326</v>
+        <v>7453323</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,10 +9927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294738</v>
+        <v>122294739</v>
       </c>
       <c r="B83" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>759436</v>
+        <v>759446</v>
       </c>
       <c r="R83" t="n">
-        <v>7453325</v>
+        <v>7453342</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,10 +10048,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294754</v>
+        <v>122294755</v>
       </c>
       <c r="B84" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>760088</v>
+        <v>760091</v>
       </c>
       <c r="R84" t="n">
-        <v>7452640</v>
+        <v>7452637</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,10 +10169,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294735</v>
+        <v>122294738</v>
       </c>
       <c r="B85" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759441</v>
+        <v>759436</v>
       </c>
       <c r="R85" t="n">
-        <v>7453256</v>
+        <v>7453325</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,10 +10290,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294737</v>
+        <v>122294750</v>
       </c>
       <c r="B86" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759443</v>
+        <v>759475</v>
       </c>
       <c r="R86" t="n">
-        <v>7453255</v>
+        <v>7453308</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,10 +10411,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294750</v>
+        <v>122294745</v>
       </c>
       <c r="B87" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>759475</v>
+        <v>759454</v>
       </c>
       <c r="R87" t="n">
-        <v>7453308</v>
+        <v>7453307</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,10 +10532,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294732</v>
+        <v>122294749</v>
       </c>
       <c r="B88" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759420</v>
+        <v>759478</v>
       </c>
       <c r="R88" t="n">
-        <v>7453262</v>
+        <v>7453303</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294748</v>
+        <v>122294744</v>
       </c>
       <c r="B89" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>759459</v>
+        <v>759458</v>
       </c>
       <c r="R89" t="n">
-        <v>7453317</v>
+        <v>7453299</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294741</v>
+        <v>122294740</v>
       </c>
       <c r="B90" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759446</v>
+        <v>759438</v>
       </c>
       <c r="R90" t="n">
-        <v>7453323</v>
+        <v>7453321</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,10 +10895,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294736</v>
+        <v>122294746</v>
       </c>
       <c r="B91" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759442</v>
+        <v>759454</v>
       </c>
       <c r="R91" t="n">
-        <v>7453258</v>
+        <v>7453310</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294733</v>
+        <v>122294666</v>
       </c>
       <c r="B92" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>759435</v>
+        <v>759423</v>
       </c>
       <c r="R92" t="n">
-        <v>7453258</v>
+        <v>7453284</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11100,17 +11100,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,10 +11137,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294743</v>
+        <v>122294748</v>
       </c>
       <c r="B93" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759443</v>
+        <v>759459</v>
       </c>
       <c r="R93" t="n">
-        <v>7453311</v>
+        <v>7453317</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,10 +11258,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294753</v>
+        <v>122294751</v>
       </c>
       <c r="B94" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759466</v>
+        <v>759473</v>
       </c>
       <c r="R94" t="n">
-        <v>7453312</v>
+        <v>7453318</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11379,10 +11379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294749</v>
+        <v>122294733</v>
       </c>
       <c r="B95" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759478</v>
+        <v>759435</v>
       </c>
       <c r="R95" t="n">
-        <v>7453303</v>
+        <v>7453258</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11500,10 +11500,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294740</v>
+        <v>122294742</v>
       </c>
       <c r="B96" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759438</v>
+        <v>759446</v>
       </c>
       <c r="R96" t="n">
-        <v>7453321</v>
+        <v>7453326</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,10 +11621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294751</v>
+        <v>122294752</v>
       </c>
       <c r="B97" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759473</v>
+        <v>759463</v>
       </c>
       <c r="R97" t="n">
-        <v>7453318</v>
+        <v>7453317</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,10 +11742,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294746</v>
+        <v>122294735</v>
       </c>
       <c r="B98" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759454</v>
+        <v>759441</v>
       </c>
       <c r="R98" t="n">
-        <v>7453310</v>
+        <v>7453256</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,10 +11863,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294666</v>
+        <v>122294737</v>
       </c>
       <c r="B99" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759423</v>
+        <v>759443</v>
       </c>
       <c r="R99" t="n">
-        <v>7453284</v>
+        <v>7453255</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11947,17 +11947,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11987,7 +11987,7 @@
         <v>122294734</v>
       </c>
       <c r="B100" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12105,10 +12105,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294744</v>
+        <v>122294736</v>
       </c>
       <c r="B101" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12159,10 +12159,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759458</v>
+        <v>759442</v>
       </c>
       <c r="R101" t="n">
-        <v>7453299</v>
+        <v>7453258</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12226,10 +12226,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294745</v>
+        <v>122294753</v>
       </c>
       <c r="B102" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759454</v>
+        <v>759466</v>
       </c>
       <c r="R102" t="n">
-        <v>7453307</v>
+        <v>7453312</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12347,10 +12347,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294755</v>
+        <v>122294732</v>
       </c>
       <c r="B103" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>760091</v>
+        <v>759420</v>
       </c>
       <c r="R103" t="n">
-        <v>7452637</v>
+        <v>7453262</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12431,17 +12431,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12468,10 +12468,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294752</v>
+        <v>122294754</v>
       </c>
       <c r="B104" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>759463</v>
+        <v>760088</v>
       </c>
       <c r="R104" t="n">
-        <v>7453317</v>
+        <v>7452640</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12552,17 +12552,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12589,10 +12589,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294739</v>
+        <v>122294743</v>
       </c>
       <c r="B105" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759446</v>
+        <v>759443</v>
       </c>
       <c r="R105" t="n">
-        <v>7453342</v>
+        <v>7453311</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,10 +9806,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294741</v>
+        <v>122294752</v>
       </c>
       <c r="B82" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>759446</v>
+        <v>759463</v>
       </c>
       <c r="R82" t="n">
-        <v>7453323</v>
+        <v>7453317</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,10 +9927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294739</v>
+        <v>122294747</v>
       </c>
       <c r="B83" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>759446</v>
+        <v>759454</v>
       </c>
       <c r="R83" t="n">
-        <v>7453342</v>
+        <v>7453307</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,10 +10048,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294755</v>
+        <v>122294733</v>
       </c>
       <c r="B84" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>760091</v>
+        <v>759435</v>
       </c>
       <c r="R84" t="n">
-        <v>7452637</v>
+        <v>7453258</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10132,17 +10132,17 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,10 +10169,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294738</v>
+        <v>122294737</v>
       </c>
       <c r="B85" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759436</v>
+        <v>759443</v>
       </c>
       <c r="R85" t="n">
-        <v>7453325</v>
+        <v>7453255</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,10 +10290,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294750</v>
+        <v>122294742</v>
       </c>
       <c r="B86" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759475</v>
+        <v>759446</v>
       </c>
       <c r="R86" t="n">
-        <v>7453308</v>
+        <v>7453326</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,10 +10411,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294745</v>
+        <v>122294748</v>
       </c>
       <c r="B87" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>759454</v>
+        <v>759459</v>
       </c>
       <c r="R87" t="n">
-        <v>7453307</v>
+        <v>7453317</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,10 +10532,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294749</v>
+        <v>122294750</v>
       </c>
       <c r="B88" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759478</v>
+        <v>759475</v>
       </c>
       <c r="R88" t="n">
-        <v>7453303</v>
+        <v>7453308</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294744</v>
+        <v>122294738</v>
       </c>
       <c r="B89" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>759458</v>
+        <v>759436</v>
       </c>
       <c r="R89" t="n">
-        <v>7453299</v>
+        <v>7453325</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294740</v>
+        <v>122294739</v>
       </c>
       <c r="B90" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759438</v>
+        <v>759446</v>
       </c>
       <c r="R90" t="n">
-        <v>7453321</v>
+        <v>7453342</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,10 +10895,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294746</v>
+        <v>122294740</v>
       </c>
       <c r="B91" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759454</v>
+        <v>759438</v>
       </c>
       <c r="R91" t="n">
-        <v>7453310</v>
+        <v>7453321</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294666</v>
+        <v>122294754</v>
       </c>
       <c r="B92" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>759423</v>
+        <v>760088</v>
       </c>
       <c r="R92" t="n">
-        <v>7453284</v>
+        <v>7452640</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11100,17 +11100,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,10 +11137,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294748</v>
+        <v>122294743</v>
       </c>
       <c r="B93" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759459</v>
+        <v>759443</v>
       </c>
       <c r="R93" t="n">
-        <v>7453317</v>
+        <v>7453311</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,10 +11258,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294751</v>
+        <v>122294741</v>
       </c>
       <c r="B94" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759473</v>
+        <v>759446</v>
       </c>
       <c r="R94" t="n">
-        <v>7453318</v>
+        <v>7453323</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11379,10 +11379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294733</v>
+        <v>122294751</v>
       </c>
       <c r="B95" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759435</v>
+        <v>759473</v>
       </c>
       <c r="R95" t="n">
-        <v>7453258</v>
+        <v>7453318</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11500,10 +11500,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294742</v>
+        <v>122294736</v>
       </c>
       <c r="B96" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759446</v>
+        <v>759442</v>
       </c>
       <c r="R96" t="n">
-        <v>7453326</v>
+        <v>7453258</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,10 +11621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294752</v>
+        <v>122294734</v>
       </c>
       <c r="B97" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759463</v>
+        <v>759440</v>
       </c>
       <c r="R97" t="n">
-        <v>7453317</v>
+        <v>7453257</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,10 +11742,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294735</v>
+        <v>122294749</v>
       </c>
       <c r="B98" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759441</v>
+        <v>759478</v>
       </c>
       <c r="R98" t="n">
-        <v>7453256</v>
+        <v>7453303</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,10 +11863,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294737</v>
+        <v>122294732</v>
       </c>
       <c r="B99" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759443</v>
+        <v>759420</v>
       </c>
       <c r="R99" t="n">
-        <v>7453255</v>
+        <v>7453262</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11984,10 +11984,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294734</v>
+        <v>122294666</v>
       </c>
       <c r="B100" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12038,10 +12038,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>759440</v>
+        <v>759423</v>
       </c>
       <c r="R100" t="n">
-        <v>7453257</v>
+        <v>7453284</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12068,17 +12068,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12105,10 +12105,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294736</v>
+        <v>122294753</v>
       </c>
       <c r="B101" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12159,10 +12159,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759442</v>
+        <v>759466</v>
       </c>
       <c r="R101" t="n">
-        <v>7453258</v>
+        <v>7453312</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12226,10 +12226,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294753</v>
+        <v>122294735</v>
       </c>
       <c r="B102" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759466</v>
+        <v>759441</v>
       </c>
       <c r="R102" t="n">
-        <v>7453312</v>
+        <v>7453256</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12347,10 +12347,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294732</v>
+        <v>122294755</v>
       </c>
       <c r="B103" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>759420</v>
+        <v>760091</v>
       </c>
       <c r="R103" t="n">
-        <v>7453262</v>
+        <v>7452637</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12431,17 +12431,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12468,10 +12468,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294754</v>
+        <v>122294744</v>
       </c>
       <c r="B104" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>760088</v>
+        <v>759458</v>
       </c>
       <c r="R104" t="n">
-        <v>7452640</v>
+        <v>7453299</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12552,17 +12552,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12589,10 +12589,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294743</v>
+        <v>122294746</v>
       </c>
       <c r="B105" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759443</v>
+        <v>759454</v>
       </c>
       <c r="R105" t="n">
-        <v>7453311</v>
+        <v>7453310</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -11137,7 +11137,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294743</v>
+        <v>122294741</v>
       </c>
       <c r="B93" t="n">
         <v>98202</v>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759443</v>
+        <v>759446</v>
       </c>
       <c r="R93" t="n">
-        <v>7453311</v>
+        <v>7453323</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,7 +11258,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294741</v>
+        <v>122294743</v>
       </c>
       <c r="B94" t="n">
         <v>98202</v>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759446</v>
+        <v>759443</v>
       </c>
       <c r="R94" t="n">
-        <v>7453323</v>
+        <v>7453311</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,10 +9806,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294752</v>
+        <v>122294666</v>
       </c>
       <c r="B82" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9824,11 +9824,6 @@
       <c r="E82" t="n">
         <v>220787</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -9841,7 +9836,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9860,10 +9855,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>759463</v>
+        <v>759423</v>
       </c>
       <c r="R82" t="n">
-        <v>7453317</v>
+        <v>7453284</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9890,17 +9885,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,10 +9922,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294747</v>
+        <v>122294740</v>
       </c>
       <c r="B83" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9945,11 +9940,6 @@
       <c r="E83" t="n">
         <v>220787</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -9962,7 +9952,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9971,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>759454</v>
+        <v>759438</v>
       </c>
       <c r="R83" t="n">
-        <v>7453307</v>
+        <v>7453321</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10021,7 +10011,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,10 +10038,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294733</v>
+        <v>122294741</v>
       </c>
       <c r="B84" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10066,11 +10056,6 @@
       <c r="E84" t="n">
         <v>220787</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10083,7 +10068,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10102,10 +10087,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>759435</v>
+        <v>759446</v>
       </c>
       <c r="R84" t="n">
-        <v>7453258</v>
+        <v>7453323</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10142,7 +10127,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,10 +10154,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294737</v>
+        <v>122294732</v>
       </c>
       <c r="B85" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10187,11 +10172,6 @@
       <c r="E85" t="n">
         <v>220787</v>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10204,7 +10184,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10203,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759443</v>
+        <v>759420</v>
       </c>
       <c r="R85" t="n">
-        <v>7453255</v>
+        <v>7453262</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10243,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,10 +10270,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294742</v>
+        <v>122294738</v>
       </c>
       <c r="B86" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10308,11 +10288,6 @@
       <c r="E86" t="n">
         <v>220787</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10325,7 +10300,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10319,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759446</v>
+        <v>759436</v>
       </c>
       <c r="R86" t="n">
-        <v>7453326</v>
+        <v>7453325</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10384,7 +10359,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,10 +10386,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294748</v>
+        <v>122294752</v>
       </c>
       <c r="B87" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10429,11 +10404,6 @@
       <c r="E87" t="n">
         <v>220787</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10446,7 +10416,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,7 +10435,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>759459</v>
+        <v>759463</v>
       </c>
       <c r="R87" t="n">
         <v>7453317</v>
@@ -10505,7 +10475,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,10 +10502,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294750</v>
+        <v>122294743</v>
       </c>
       <c r="B88" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10550,11 +10520,6 @@
       <c r="E88" t="n">
         <v>220787</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10567,7 +10532,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10551,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759475</v>
+        <v>759443</v>
       </c>
       <c r="R88" t="n">
-        <v>7453308</v>
+        <v>7453311</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10626,7 +10591,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,10 +10618,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294738</v>
+        <v>122294754</v>
       </c>
       <c r="B89" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10671,11 +10636,6 @@
       <c r="E89" t="n">
         <v>220787</v>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10688,7 +10648,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10667,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>759436</v>
+        <v>760088</v>
       </c>
       <c r="R89" t="n">
-        <v>7453325</v>
+        <v>7452640</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10737,17 +10697,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10777,7 +10737,7 @@
         <v>122294739</v>
       </c>
       <c r="B90" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10791,11 +10751,6 @@
       </c>
       <c r="E90" t="n">
         <v>220787</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -10895,10 +10850,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294740</v>
+        <v>122294753</v>
       </c>
       <c r="B91" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10913,11 +10868,6 @@
       <c r="E91" t="n">
         <v>220787</v>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10930,7 +10880,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10899,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759438</v>
+        <v>759466</v>
       </c>
       <c r="R91" t="n">
-        <v>7453321</v>
+        <v>7453312</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10939,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,10 +10966,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294754</v>
+        <v>122294750</v>
       </c>
       <c r="B92" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11034,11 +10984,6 @@
       <c r="E92" t="n">
         <v>220787</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11051,7 +10996,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11015,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>760088</v>
+        <v>759475</v>
       </c>
       <c r="R92" t="n">
-        <v>7452640</v>
+        <v>7453308</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11100,17 +11045,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,10 +11082,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294741</v>
+        <v>122294742</v>
       </c>
       <c r="B93" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11155,11 +11100,6 @@
       <c r="E93" t="n">
         <v>220787</v>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11172,7 +11112,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11194,7 +11134,7 @@
         <v>759446</v>
       </c>
       <c r="R93" t="n">
-        <v>7453323</v>
+        <v>7453326</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11171,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,10 +11198,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294743</v>
+        <v>122294733</v>
       </c>
       <c r="B94" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11276,11 +11216,6 @@
       <c r="E94" t="n">
         <v>220787</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11293,7 +11228,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11247,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759443</v>
+        <v>759435</v>
       </c>
       <c r="R94" t="n">
-        <v>7453311</v>
+        <v>7453258</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11287,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11382,7 +11317,7 @@
         <v>122294751</v>
       </c>
       <c r="B95" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11396,11 +11331,6 @@
       </c>
       <c r="E95" t="n">
         <v>220787</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -11500,10 +11430,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294736</v>
+        <v>122294748</v>
       </c>
       <c r="B96" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11518,11 +11448,6 @@
       <c r="E96" t="n">
         <v>220787</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11535,7 +11460,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11479,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759442</v>
+        <v>759459</v>
       </c>
       <c r="R96" t="n">
-        <v>7453258</v>
+        <v>7453317</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11594,7 +11519,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,10 +11546,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294734</v>
+        <v>122294736</v>
       </c>
       <c r="B97" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11639,11 +11564,6 @@
       <c r="E97" t="n">
         <v>220787</v>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11656,7 +11576,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11595,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759440</v>
+        <v>759442</v>
       </c>
       <c r="R97" t="n">
-        <v>7453257</v>
+        <v>7453258</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11715,7 +11635,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,10 +11662,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294749</v>
+        <v>122294746</v>
       </c>
       <c r="B98" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11760,11 +11680,6 @@
       <c r="E98" t="n">
         <v>220787</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11777,7 +11692,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11711,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759478</v>
+        <v>759454</v>
       </c>
       <c r="R98" t="n">
-        <v>7453303</v>
+        <v>7453310</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11751,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,10 +11778,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294732</v>
+        <v>122294737</v>
       </c>
       <c r="B99" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11881,11 +11796,6 @@
       <c r="E99" t="n">
         <v>220787</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11898,7 +11808,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11827,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759420</v>
+        <v>759443</v>
       </c>
       <c r="R99" t="n">
-        <v>7453262</v>
+        <v>7453255</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11957,7 +11867,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11984,10 +11894,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294666</v>
+        <v>122294755</v>
       </c>
       <c r="B100" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12002,11 +11912,6 @@
       <c r="E100" t="n">
         <v>220787</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12019,7 +11924,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12038,10 +11943,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>759423</v>
+        <v>760091</v>
       </c>
       <c r="R100" t="n">
-        <v>7453284</v>
+        <v>7452637</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12068,17 +11973,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12105,10 +12010,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294753</v>
+        <v>122294735</v>
       </c>
       <c r="B101" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12123,11 +12028,6 @@
       <c r="E101" t="n">
         <v>220787</v>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12140,7 +12040,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12159,10 +12059,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759466</v>
+        <v>759441</v>
       </c>
       <c r="R101" t="n">
-        <v>7453312</v>
+        <v>7453256</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12199,7 +12099,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12226,10 +12126,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294735</v>
+        <v>122294734</v>
       </c>
       <c r="B102" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12244,11 +12144,6 @@
       <c r="E102" t="n">
         <v>220787</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12261,7 +12156,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12175,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759441</v>
+        <v>759440</v>
       </c>
       <c r="R102" t="n">
-        <v>7453256</v>
+        <v>7453257</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12215,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12347,10 +12242,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294755</v>
+        <v>122294744</v>
       </c>
       <c r="B103" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12365,11 +12260,6 @@
       <c r="E103" t="n">
         <v>220787</v>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12382,7 +12272,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12401,10 +12291,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>760091</v>
+        <v>759458</v>
       </c>
       <c r="R103" t="n">
-        <v>7452637</v>
+        <v>7453299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12431,17 +12321,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12468,10 +12358,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294744</v>
+        <v>122294745</v>
       </c>
       <c r="B104" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12486,11 +12376,6 @@
       <c r="E104" t="n">
         <v>220787</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12503,7 +12388,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12522,10 +12407,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>759458</v>
+        <v>759454</v>
       </c>
       <c r="R104" t="n">
-        <v>7453299</v>
+        <v>7453307</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12562,7 +12447,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12589,10 +12474,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294746</v>
+        <v>122294749</v>
       </c>
       <c r="B105" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12607,11 +12492,6 @@
       <c r="E105" t="n">
         <v>220787</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12624,7 +12504,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12523,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759454</v>
+        <v>759478</v>
       </c>
       <c r="R105" t="n">
-        <v>7453310</v>
+        <v>7453303</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12683,7 +12563,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,10 +9806,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294666</v>
+        <v>122294746</v>
       </c>
       <c r="B82" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9824,6 +9824,11 @@
       <c r="E82" t="n">
         <v>220787</v>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -9836,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9855,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>759423</v>
+        <v>759454</v>
       </c>
       <c r="R82" t="n">
-        <v>7453284</v>
+        <v>7453310</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9885,17 +9890,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9922,10 +9927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294740</v>
+        <v>122294736</v>
       </c>
       <c r="B83" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9940,6 +9945,11 @@
       <c r="E83" t="n">
         <v>220787</v>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -9952,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9971,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>759438</v>
+        <v>759442</v>
       </c>
       <c r="R83" t="n">
-        <v>7453321</v>
+        <v>7453258</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10011,7 +10021,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10038,10 +10048,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294741</v>
+        <v>122294740</v>
       </c>
       <c r="B84" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10056,6 +10066,11 @@
       <c r="E84" t="n">
         <v>220787</v>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10068,7 +10083,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10087,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>759446</v>
+        <v>759438</v>
       </c>
       <c r="R84" t="n">
-        <v>7453323</v>
+        <v>7453321</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10127,7 +10142,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10154,10 +10169,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294732</v>
+        <v>122294747</v>
       </c>
       <c r="B85" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10172,6 +10187,11 @@
       <c r="E85" t="n">
         <v>220787</v>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10184,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10203,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759420</v>
+        <v>759454</v>
       </c>
       <c r="R85" t="n">
-        <v>7453262</v>
+        <v>7453307</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10243,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10270,10 +10290,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294738</v>
+        <v>122294743</v>
       </c>
       <c r="B86" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10288,6 +10308,11 @@
       <c r="E86" t="n">
         <v>220787</v>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10300,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10319,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759436</v>
+        <v>759443</v>
       </c>
       <c r="R86" t="n">
-        <v>7453325</v>
+        <v>7453311</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10359,7 +10384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10389,7 +10414,7 @@
         <v>122294752</v>
       </c>
       <c r="B87" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10403,6 +10428,11 @@
       </c>
       <c r="E87" t="n">
         <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10502,10 +10532,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294743</v>
+        <v>122294750</v>
       </c>
       <c r="B88" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10520,6 +10550,11 @@
       <c r="E88" t="n">
         <v>220787</v>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10532,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10551,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759443</v>
+        <v>759475</v>
       </c>
       <c r="R88" t="n">
-        <v>7453311</v>
+        <v>7453308</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10591,7 +10626,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10621,7 +10656,7 @@
         <v>122294754</v>
       </c>
       <c r="B89" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10635,6 +10670,11 @@
       </c>
       <c r="E89" t="n">
         <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -10734,10 +10774,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294739</v>
+        <v>122294753</v>
       </c>
       <c r="B90" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10752,6 +10792,11 @@
       <c r="E90" t="n">
         <v>220787</v>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10764,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10783,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759446</v>
+        <v>759466</v>
       </c>
       <c r="R90" t="n">
-        <v>7453342</v>
+        <v>7453312</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10823,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10850,10 +10895,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294753</v>
+        <v>122294748</v>
       </c>
       <c r="B91" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10868,6 +10913,11 @@
       <c r="E91" t="n">
         <v>220787</v>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10880,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10899,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759466</v>
+        <v>759459</v>
       </c>
       <c r="R91" t="n">
-        <v>7453312</v>
+        <v>7453317</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10939,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10966,10 +11016,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294750</v>
+        <v>122294755</v>
       </c>
       <c r="B92" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10984,6 +11034,11 @@
       <c r="E92" t="n">
         <v>220787</v>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -10996,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11015,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>759475</v>
+        <v>760091</v>
       </c>
       <c r="R92" t="n">
-        <v>7453308</v>
+        <v>7452637</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11045,17 +11100,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11082,10 +11137,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294742</v>
+        <v>122294737</v>
       </c>
       <c r="B93" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11100,6 +11155,11 @@
       <c r="E93" t="n">
         <v>220787</v>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11112,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11131,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759446</v>
+        <v>759443</v>
       </c>
       <c r="R93" t="n">
-        <v>7453326</v>
+        <v>7453255</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11171,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11198,10 +11258,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294733</v>
+        <v>122294738</v>
       </c>
       <c r="B94" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11216,6 +11276,11 @@
       <c r="E94" t="n">
         <v>220787</v>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11228,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11247,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759435</v>
+        <v>759436</v>
       </c>
       <c r="R94" t="n">
-        <v>7453258</v>
+        <v>7453325</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11287,7 +11352,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11314,10 +11379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294751</v>
+        <v>122294733</v>
       </c>
       <c r="B95" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11332,6 +11397,11 @@
       <c r="E95" t="n">
         <v>220787</v>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11344,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11363,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759473</v>
+        <v>759435</v>
       </c>
       <c r="R95" t="n">
-        <v>7453318</v>
+        <v>7453258</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11403,7 +11473,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11430,10 +11500,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294748</v>
+        <v>122294666</v>
       </c>
       <c r="B96" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11448,6 +11518,11 @@
       <c r="E96" t="n">
         <v>220787</v>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11460,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11479,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759459</v>
+        <v>759423</v>
       </c>
       <c r="R96" t="n">
-        <v>7453317</v>
+        <v>7453284</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11509,17 +11584,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11546,10 +11621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294736</v>
+        <v>122294742</v>
       </c>
       <c r="B97" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11564,6 +11639,11 @@
       <c r="E97" t="n">
         <v>220787</v>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11576,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11595,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759442</v>
+        <v>759446</v>
       </c>
       <c r="R97" t="n">
-        <v>7453258</v>
+        <v>7453326</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11635,7 +11715,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11662,10 +11742,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294746</v>
+        <v>122294744</v>
       </c>
       <c r="B98" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11680,6 +11760,11 @@
       <c r="E98" t="n">
         <v>220787</v>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11692,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11711,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759454</v>
+        <v>759458</v>
       </c>
       <c r="R98" t="n">
-        <v>7453310</v>
+        <v>7453299</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11751,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11778,10 +11863,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294737</v>
+        <v>122294732</v>
       </c>
       <c r="B99" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11796,6 +11881,11 @@
       <c r="E99" t="n">
         <v>220787</v>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11808,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11827,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759443</v>
+        <v>759420</v>
       </c>
       <c r="R99" t="n">
-        <v>7453255</v>
+        <v>7453262</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11867,7 +11957,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11894,10 +11984,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294755</v>
+        <v>122294734</v>
       </c>
       <c r="B100" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11912,6 +12002,11 @@
       <c r="E100" t="n">
         <v>220787</v>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -11924,7 +12019,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -11943,10 +12038,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>760091</v>
+        <v>759440</v>
       </c>
       <c r="R100" t="n">
-        <v>7452637</v>
+        <v>7453257</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11973,17 +12068,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12010,10 +12105,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294735</v>
+        <v>122294751</v>
       </c>
       <c r="B101" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12028,6 +12123,11 @@
       <c r="E101" t="n">
         <v>220787</v>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12040,7 +12140,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12059,10 +12159,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759441</v>
+        <v>759473</v>
       </c>
       <c r="R101" t="n">
-        <v>7453256</v>
+        <v>7453318</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12099,7 +12199,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12126,10 +12226,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294734</v>
+        <v>122294741</v>
       </c>
       <c r="B102" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12144,6 +12244,11 @@
       <c r="E102" t="n">
         <v>220787</v>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12156,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12175,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759440</v>
+        <v>759446</v>
       </c>
       <c r="R102" t="n">
-        <v>7453257</v>
+        <v>7453323</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12215,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12242,10 +12347,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294744</v>
+        <v>122294749</v>
       </c>
       <c r="B103" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12260,6 +12365,11 @@
       <c r="E103" t="n">
         <v>220787</v>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12272,7 +12382,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12291,10 +12401,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>759458</v>
+        <v>759478</v>
       </c>
       <c r="R103" t="n">
-        <v>7453299</v>
+        <v>7453303</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12331,7 +12441,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12358,10 +12468,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294745</v>
+        <v>122294735</v>
       </c>
       <c r="B104" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12376,6 +12486,11 @@
       <c r="E104" t="n">
         <v>220787</v>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12388,7 +12503,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12407,10 +12522,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>759454</v>
+        <v>759441</v>
       </c>
       <c r="R104" t="n">
-        <v>7453307</v>
+        <v>7453256</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12447,7 +12562,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12474,10 +12589,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294749</v>
+        <v>122294739</v>
       </c>
       <c r="B105" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12492,6 +12607,11 @@
       <c r="E105" t="n">
         <v>220787</v>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -12504,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12523,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759478</v>
+        <v>759446</v>
       </c>
       <c r="R105" t="n">
-        <v>7453303</v>
+        <v>7453342</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12563,7 +12683,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,10 +9806,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294746</v>
+        <v>122294755</v>
       </c>
       <c r="B82" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>759454</v>
+        <v>760091</v>
       </c>
       <c r="R82" t="n">
-        <v>7453310</v>
+        <v>7452637</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9890,17 +9890,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,10 +9927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294736</v>
+        <v>122294746</v>
       </c>
       <c r="B83" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>759442</v>
+        <v>759454</v>
       </c>
       <c r="R83" t="n">
-        <v>7453258</v>
+        <v>7453310</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,10 +10048,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294740</v>
+        <v>122294751</v>
       </c>
       <c r="B84" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>759438</v>
+        <v>759473</v>
       </c>
       <c r="R84" t="n">
-        <v>7453321</v>
+        <v>7453318</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,10 +10169,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294747</v>
+        <v>122294732</v>
       </c>
       <c r="B85" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759454</v>
+        <v>759420</v>
       </c>
       <c r="R85" t="n">
-        <v>7453307</v>
+        <v>7453262</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,10 +10290,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294743</v>
+        <v>122294748</v>
       </c>
       <c r="B86" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759443</v>
+        <v>759459</v>
       </c>
       <c r="R86" t="n">
-        <v>7453311</v>
+        <v>7453317</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,10 +10411,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294752</v>
+        <v>122294742</v>
       </c>
       <c r="B87" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>759463</v>
+        <v>759446</v>
       </c>
       <c r="R87" t="n">
-        <v>7453317</v>
+        <v>7453326</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,10 +10532,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294750</v>
+        <v>122294743</v>
       </c>
       <c r="B88" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759475</v>
+        <v>759443</v>
       </c>
       <c r="R88" t="n">
-        <v>7453308</v>
+        <v>7453311</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294754</v>
+        <v>122294744</v>
       </c>
       <c r="B89" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>760088</v>
+        <v>759458</v>
       </c>
       <c r="R89" t="n">
-        <v>7452640</v>
+        <v>7453299</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10737,17 +10737,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294753</v>
+        <v>122294750</v>
       </c>
       <c r="B90" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759466</v>
+        <v>759475</v>
       </c>
       <c r="R90" t="n">
-        <v>7453312</v>
+        <v>7453308</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,10 +10895,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294748</v>
+        <v>122294745</v>
       </c>
       <c r="B91" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759459</v>
+        <v>759454</v>
       </c>
       <c r="R91" t="n">
-        <v>7453317</v>
+        <v>7453307</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294755</v>
+        <v>122294737</v>
       </c>
       <c r="B92" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>760091</v>
+        <v>759443</v>
       </c>
       <c r="R92" t="n">
-        <v>7452637</v>
+        <v>7453255</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11100,17 +11100,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,10 +11137,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294737</v>
+        <v>122294734</v>
       </c>
       <c r="B93" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759443</v>
+        <v>759440</v>
       </c>
       <c r="R93" t="n">
-        <v>7453255</v>
+        <v>7453257</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,10 +11258,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294738</v>
+        <v>122294740</v>
       </c>
       <c r="B94" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759436</v>
+        <v>759438</v>
       </c>
       <c r="R94" t="n">
-        <v>7453325</v>
+        <v>7453321</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11379,10 +11379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294733</v>
+        <v>122294738</v>
       </c>
       <c r="B95" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759435</v>
+        <v>759436</v>
       </c>
       <c r="R95" t="n">
-        <v>7453258</v>
+        <v>7453325</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11500,10 +11500,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294666</v>
+        <v>122294741</v>
       </c>
       <c r="B96" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759423</v>
+        <v>759446</v>
       </c>
       <c r="R96" t="n">
-        <v>7453284</v>
+        <v>7453323</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11584,17 +11584,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,10 +11621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294742</v>
+        <v>122294736</v>
       </c>
       <c r="B97" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759446</v>
+        <v>759442</v>
       </c>
       <c r="R97" t="n">
-        <v>7453326</v>
+        <v>7453258</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,10 +11742,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294744</v>
+        <v>122294733</v>
       </c>
       <c r="B98" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759458</v>
+        <v>759435</v>
       </c>
       <c r="R98" t="n">
-        <v>7453299</v>
+        <v>7453258</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,10 +11863,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294732</v>
+        <v>122294754</v>
       </c>
       <c r="B99" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759420</v>
+        <v>760088</v>
       </c>
       <c r="R99" t="n">
-        <v>7453262</v>
+        <v>7452640</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11947,17 +11947,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11984,10 +11984,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294734</v>
+        <v>122294739</v>
       </c>
       <c r="B100" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12038,10 +12038,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>759440</v>
+        <v>759446</v>
       </c>
       <c r="R100" t="n">
-        <v>7453257</v>
+        <v>7453342</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12105,10 +12105,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294751</v>
+        <v>122294752</v>
       </c>
       <c r="B101" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12159,10 +12159,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759473</v>
+        <v>759463</v>
       </c>
       <c r="R101" t="n">
-        <v>7453318</v>
+        <v>7453317</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12226,10 +12226,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294741</v>
+        <v>122294753</v>
       </c>
       <c r="B102" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759446</v>
+        <v>759466</v>
       </c>
       <c r="R102" t="n">
-        <v>7453323</v>
+        <v>7453312</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12350,7 +12350,7 @@
         <v>122294749</v>
       </c>
       <c r="B103" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>122294735</v>
       </c>
       <c r="B104" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12589,10 +12589,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294739</v>
+        <v>122294666</v>
       </c>
       <c r="B105" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759446</v>
+        <v>759423</v>
       </c>
       <c r="R105" t="n">
-        <v>7453342</v>
+        <v>7453284</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12673,17 +12673,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,7 +9806,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294755</v>
+        <v>122294666</v>
       </c>
       <c r="B82" t="n">
         <v>98237</v>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>760091</v>
+        <v>759423</v>
       </c>
       <c r="R82" t="n">
-        <v>7452637</v>
+        <v>7453284</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9890,17 +9890,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,7 +9927,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294746</v>
+        <v>122294743</v>
       </c>
       <c r="B83" t="n">
         <v>98237</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>759454</v>
+        <v>759443</v>
       </c>
       <c r="R83" t="n">
-        <v>7453310</v>
+        <v>7453311</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,7 +10048,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294751</v>
+        <v>122294735</v>
       </c>
       <c r="B84" t="n">
         <v>98237</v>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>759473</v>
+        <v>759441</v>
       </c>
       <c r="R84" t="n">
-        <v>7453318</v>
+        <v>7453256</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,7 +10169,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294732</v>
+        <v>122294749</v>
       </c>
       <c r="B85" t="n">
         <v>98237</v>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759420</v>
+        <v>759478</v>
       </c>
       <c r="R85" t="n">
-        <v>7453262</v>
+        <v>7453303</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,7 +10290,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294748</v>
+        <v>122294740</v>
       </c>
       <c r="B86" t="n">
         <v>98237</v>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759459</v>
+        <v>759438</v>
       </c>
       <c r="R86" t="n">
-        <v>7453317</v>
+        <v>7453321</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,7 +10411,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294742</v>
+        <v>122294733</v>
       </c>
       <c r="B87" t="n">
         <v>98237</v>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>759446</v>
+        <v>759435</v>
       </c>
       <c r="R87" t="n">
-        <v>7453326</v>
+        <v>7453258</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,7 +10532,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294743</v>
+        <v>122294742</v>
       </c>
       <c r="B88" t="n">
         <v>98237</v>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759443</v>
+        <v>759446</v>
       </c>
       <c r="R88" t="n">
-        <v>7453311</v>
+        <v>7453326</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,7 +10653,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294744</v>
+        <v>122294748</v>
       </c>
       <c r="B89" t="n">
         <v>98237</v>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>759458</v>
+        <v>759459</v>
       </c>
       <c r="R89" t="n">
-        <v>7453299</v>
+        <v>7453317</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10774,7 +10774,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294750</v>
+        <v>122294753</v>
       </c>
       <c r="B90" t="n">
         <v>98237</v>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759475</v>
+        <v>759466</v>
       </c>
       <c r="R90" t="n">
-        <v>7453308</v>
+        <v>7453312</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,7 +10895,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294745</v>
+        <v>122294732</v>
       </c>
       <c r="B91" t="n">
         <v>98237</v>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759454</v>
+        <v>759420</v>
       </c>
       <c r="R91" t="n">
-        <v>7453307</v>
+        <v>7453262</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,7 +11016,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294737</v>
+        <v>122294738</v>
       </c>
       <c r="B92" t="n">
         <v>98237</v>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>759443</v>
+        <v>759436</v>
       </c>
       <c r="R92" t="n">
-        <v>7453255</v>
+        <v>7453325</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,7 +11137,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294734</v>
+        <v>122294747</v>
       </c>
       <c r="B93" t="n">
         <v>98237</v>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759440</v>
+        <v>759454</v>
       </c>
       <c r="R93" t="n">
-        <v>7453257</v>
+        <v>7453307</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,7 +11258,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294740</v>
+        <v>122294750</v>
       </c>
       <c r="B94" t="n">
         <v>98237</v>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759438</v>
+        <v>759475</v>
       </c>
       <c r="R94" t="n">
-        <v>7453321</v>
+        <v>7453308</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11379,7 +11379,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294738</v>
+        <v>122294746</v>
       </c>
       <c r="B95" t="n">
         <v>98237</v>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759436</v>
+        <v>759454</v>
       </c>
       <c r="R95" t="n">
-        <v>7453325</v>
+        <v>7453310</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11500,7 +11500,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294741</v>
+        <v>122294751</v>
       </c>
       <c r="B96" t="n">
         <v>98237</v>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759446</v>
+        <v>759473</v>
       </c>
       <c r="R96" t="n">
-        <v>7453323</v>
+        <v>7453318</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,7 +11621,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294736</v>
+        <v>122294755</v>
       </c>
       <c r="B97" t="n">
         <v>98237</v>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>759442</v>
+        <v>760091</v>
       </c>
       <c r="R97" t="n">
-        <v>7453258</v>
+        <v>7452637</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11705,17 +11705,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,7 +11742,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294733</v>
+        <v>122294741</v>
       </c>
       <c r="B98" t="n">
         <v>98237</v>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759435</v>
+        <v>759446</v>
       </c>
       <c r="R98" t="n">
-        <v>7453258</v>
+        <v>7453323</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,7 +11863,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294754</v>
+        <v>122294736</v>
       </c>
       <c r="B99" t="n">
         <v>98237</v>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>760088</v>
+        <v>759442</v>
       </c>
       <c r="R99" t="n">
-        <v>7452640</v>
+        <v>7453258</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11947,17 +11947,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11984,7 +11984,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294739</v>
+        <v>122294744</v>
       </c>
       <c r="B100" t="n">
         <v>98237</v>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12038,10 +12038,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>759446</v>
+        <v>759458</v>
       </c>
       <c r="R100" t="n">
-        <v>7453342</v>
+        <v>7453299</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12226,7 +12226,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294753</v>
+        <v>122294737</v>
       </c>
       <c r="B102" t="n">
         <v>98237</v>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759466</v>
+        <v>759443</v>
       </c>
       <c r="R102" t="n">
-        <v>7453312</v>
+        <v>7453255</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12347,7 +12347,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294749</v>
+        <v>122294754</v>
       </c>
       <c r="B103" t="n">
         <v>98237</v>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>759478</v>
+        <v>760088</v>
       </c>
       <c r="R103" t="n">
-        <v>7453303</v>
+        <v>7452640</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12431,17 +12431,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12468,7 +12468,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294735</v>
+        <v>122294734</v>
       </c>
       <c r="B104" t="n">
         <v>98237</v>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>759441</v>
+        <v>759440</v>
       </c>
       <c r="R104" t="n">
-        <v>7453256</v>
+        <v>7453257</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12589,7 +12589,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294666</v>
+        <v>122294739</v>
       </c>
       <c r="B105" t="n">
         <v>98237</v>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759423</v>
+        <v>759446</v>
       </c>
       <c r="R105" t="n">
-        <v>7453284</v>
+        <v>7453342</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12673,17 +12673,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 22062-2020 artfynd.xlsx
+++ b/artfynd/A 22062-2020 artfynd.xlsx
@@ -9806,10 +9806,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122294666</v>
+        <v>122294741</v>
       </c>
       <c r="B82" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>759423</v>
+        <v>759446</v>
       </c>
       <c r="R82" t="n">
-        <v>7453284</v>
+        <v>7453323</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9890,17 +9890,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9927,10 +9927,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122294743</v>
+        <v>122294752</v>
       </c>
       <c r="B83" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -9981,10 +9981,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>759443</v>
+        <v>759463</v>
       </c>
       <c r="R83" t="n">
-        <v>7453311</v>
+        <v>7453317</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10048,10 +10048,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122294735</v>
+        <v>122294737</v>
       </c>
       <c r="B84" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>759441</v>
+        <v>759443</v>
       </c>
       <c r="R84" t="n">
-        <v>7453256</v>
+        <v>7453255</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
+          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10169,10 +10169,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122294749</v>
+        <v>122294734</v>
       </c>
       <c r="B85" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>759478</v>
+        <v>759440</v>
       </c>
       <c r="R85" t="n">
-        <v>7453303</v>
+        <v>7453257</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10290,10 +10290,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122294740</v>
+        <v>122294666</v>
       </c>
       <c r="B86" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10344,10 +10344,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>759438</v>
+        <v>759423</v>
       </c>
       <c r="R86" t="n">
-        <v>7453321</v>
+        <v>7453284</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10374,17 +10374,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 17   Bladrosetter 55</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10411,10 +10411,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122294733</v>
+        <v>122294745</v>
       </c>
       <c r="B87" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>759435</v>
+        <v>759454</v>
       </c>
       <c r="R87" t="n">
-        <v>7453258</v>
+        <v>7453307</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10532,10 +10532,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122294742</v>
+        <v>122294744</v>
       </c>
       <c r="B88" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>759446</v>
+        <v>759458</v>
       </c>
       <c r="R88" t="n">
-        <v>7453326</v>
+        <v>7453299</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10653,10 +10653,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122294748</v>
+        <v>122294746</v>
       </c>
       <c r="B89" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10707,10 +10707,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>759459</v>
+        <v>759454</v>
       </c>
       <c r="R89" t="n">
-        <v>7453317</v>
+        <v>7453310</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
+          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122294753</v>
+        <v>122294751</v>
       </c>
       <c r="B90" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>759466</v>
+        <v>759473</v>
       </c>
       <c r="R90" t="n">
-        <v>7453312</v>
+        <v>7453318</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10895,10 +10895,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>122294732</v>
+        <v>122294735</v>
       </c>
       <c r="B91" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>759420</v>
+        <v>759441</v>
       </c>
       <c r="R91" t="n">
-        <v>7453262</v>
+        <v>7453256</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 4     Bladrosetter 150</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>122294738</v>
+        <v>122294736</v>
       </c>
       <c r="B92" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>759436</v>
+        <v>759442</v>
       </c>
       <c r="R92" t="n">
-        <v>7453325</v>
+        <v>7453258</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
+          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11137,10 +11137,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122294747</v>
+        <v>122294733</v>
       </c>
       <c r="B93" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>759454</v>
+        <v>759435</v>
       </c>
       <c r="R93" t="n">
-        <v>7453307</v>
+        <v>7453258</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 42   Bladrosetter 220</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 180</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11258,10 +11258,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122294750</v>
+        <v>122294738</v>
       </c>
       <c r="B94" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>759475</v>
+        <v>759436</v>
       </c>
       <c r="R94" t="n">
-        <v>7453308</v>
+        <v>7453325</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 7</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11379,10 +11379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122294746</v>
+        <v>122294754</v>
       </c>
       <c r="B95" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11433,10 +11433,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>759454</v>
+        <v>760088</v>
       </c>
       <c r="R95" t="n">
-        <v>7453310</v>
+        <v>7452640</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11463,17 +11463,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Area   1,5 x 1,0 m       Stänglar 6     Bladrosetter 60</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11500,10 +11500,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>122294751</v>
+        <v>122294740</v>
       </c>
       <c r="B96" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11554,10 +11554,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>759473</v>
+        <v>759438</v>
       </c>
       <c r="R96" t="n">
-        <v>7453318</v>
+        <v>7453321</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 24</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 2</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11621,10 +11621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>122294755</v>
+        <v>122294739</v>
       </c>
       <c r="B97" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>760091</v>
+        <v>759446</v>
       </c>
       <c r="R97" t="n">
-        <v>7452637</v>
+        <v>7453342</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11705,17 +11705,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11742,10 +11742,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122294741</v>
+        <v>122294753</v>
       </c>
       <c r="B98" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>759446</v>
+        <v>759466</v>
       </c>
       <c r="R98" t="n">
-        <v>7453323</v>
+        <v>7453312</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 40</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 1     Bladrosetter 21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11863,10 +11863,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122294736</v>
+        <v>122294743</v>
       </c>
       <c r="B99" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -11917,10 +11917,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>759442</v>
+        <v>759443</v>
       </c>
       <c r="R99" t="n">
-        <v>7453258</v>
+        <v>7453311</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Area   2,0 x 1,0 m       Stänglar 23   Bladrosetter 160</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 3     Bladrosetter 22</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11984,10 +11984,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122294744</v>
+        <v>122294755</v>
       </c>
       <c r="B100" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12038,10 +12038,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>759458</v>
+        <v>760091</v>
       </c>
       <c r="R100" t="n">
-        <v>7453299</v>
+        <v>7452637</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12068,17 +12068,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 5     Bladrosetter 21</t>
+          <t>Area   1,0 x 1,0 m       Stänglar 5     Bladrosetter 50</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12105,10 +12105,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122294752</v>
+        <v>122294742</v>
       </c>
       <c r="B101" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12159,10 +12159,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>759463</v>
+        <v>759446</v>
       </c>
       <c r="R101" t="n">
-        <v>7453317</v>
+        <v>7453326</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 2     Bladrosetter 4</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 4     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12226,10 +12226,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122294737</v>
+        <v>122294748</v>
       </c>
       <c r="B102" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>759443</v>
+        <v>759459</v>
       </c>
       <c r="R102" t="n">
-        <v>7453255</v>
+        <v>7453317</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Area   2,0 x 2,0 m       Stänglar 12   Bladrosetter 120</t>
+          <t>Area   0,5 x 0,5 m       Stänglar 7     Bladrosetter 45</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12347,10 +12347,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122294754</v>
+        <v>122294750</v>
       </c>
       <c r="B103" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12401,10 +12401,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>760088</v>
+        <v>759475</v>
       </c>
       <c r="R103" t="n">
-        <v>7452640</v>
+        <v>7453308</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12431,17 +12431,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 11   Bladrosetter 100</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 9</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12468,10 +12468,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122294734</v>
+        <v>122294732</v>
       </c>
       <c r="B104" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>759440</v>
+        <v>759420</v>
       </c>
       <c r="R104" t="n">
-        <v>7453257</v>
+        <v>7453262</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12562,7 +12562,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Area   1,0 x 1,0 m       Stänglar 7     Bladrosetter 100</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 2     Bladrosetter 40</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12589,10 +12589,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122294739</v>
+        <v>122294749</v>
       </c>
       <c r="B105" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>759446</v>
+        <v>759478</v>
       </c>
       <c r="R105" t="n">
-        <v>7453342</v>
+        <v>7453303</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Area   0,5 x 0,5 m       Stänglar 1     Bladrosetter 3</t>
+          <t>Area   0,5 x 1,0 m       Stänglar 6     Bladrosetter 80</t>
         </is>
       </c>
       <c r="AD105" t="b">
